--- a/таблицы тестирования.xlsx
+++ b/таблицы тестирования.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grigo\Documents\GitGrisha\fqw-rentAdvisor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB256C0-2427-4829-9C4C-6E48BE11284F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D2A178-D793-4A05-A263-99702DA6A26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,9 +73,6 @@
     <t>`{"suggestions":[{"address":"Тверская улица, 7","description":"Москва, Россия","latitude":55.757972,"longitude":37.611212}],"from_cache":true}`</t>
   </si>
   <si>
-    <t>✅ PASS</t>
-  </si>
-  <si>
     <t>T-02</t>
   </si>
   <si>
@@ -275,6 +272,9 @@
   </si>
   <si>
     <t>Требует ручной проверки в браузере</t>
+  </si>
+  <si>
+    <t>Успех</t>
   </si>
 </sst>
 </file>
@@ -676,7 +676,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
     <col min="2" max="2" width="31.796875" customWidth="1"/>
@@ -689,7 +689,7 @@
     <col min="9" max="9" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -718,7 +718,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -744,126 +744,126 @@
         <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -892,152 +892,152 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="I10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,123 +1066,123 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="I15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>6</v>
@@ -1211,69 +1211,69 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I7 A8:I13 A14:I18 A19:I20" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A11:I13 A16:I18 A20:H20 A5:I7 A2:H2 A3:H3 A4:H4 A8:H8 A9:H9 A10:H10 A14:H14 A15:H15 A19:H19" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>